--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E268BA-78D2-464D-A348-EF1EA758232C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A97103-73CB-4A52-B04E-00079A2935D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="184">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -695,6 +695,10 @@
   </si>
   <si>
     <t>20260430-Python-本地给图片添加水印的GUI小工具.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260506-1度电，到底能炼出多少Tokens.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2866,13 +2870,16 @@
       <c r="A11" t="s">
         <v>113</v>
       </c>
-      <c r="C11" t="e">
+      <c r="B11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" t="str">
         <f t="shared" ref="C11:C16" si="2">"- ["&amp;MID(B11,10,LEN(B11)-12)&amp;"]("&amp;A11&amp;"/"&amp;B11&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D11" t="e">
+        <v>- [1度电，到底能炼出多少Tokens](随笔/20260506-1度电，到底能炼出多少Tokens.md)</v>
+      </c>
+      <c r="D11" t="str">
         <f t="shared" ref="D11:D16" si="3">"- ["&amp;MID(B11,10,LEN(B11)-12)&amp;"](/"&amp;A11&amp;"/"&amp;B11&amp;")"</f>
-        <v>#VALUE!</v>
+        <v>- [1度电，到底能炼出多少Tokens](/随笔/20260506-1度电，到底能炼出多少Tokens.md)</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
